--- a/artfynd/A 23373-2026 artfynd.xlsx
+++ b/artfynd/A 23373-2026 artfynd.xlsx
@@ -1706,7 +1706,7 @@
         <v>136174503</v>
       </c>
       <c r="B11" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
